--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486788_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486788_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3978</v>
+        <v>0.9036</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7392</v>
+        <v>2.2632</v>
       </c>
       <c r="F3" t="n">
-        <v>1.137</v>
+        <v>-1.3596</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5054</v>
+        <v>0.3452</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.8828</v>
+        <v>0.3859</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3775</v>
+        <v>-0.0407</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4906</v>
+        <v>2.7256</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.572</v>
+        <v>2.1106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0814</v>
+        <v>0.615</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0148</v>
+        <v>-2.3804</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3109</v>
+        <v>-1.7247</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2961</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2979</v>
+        <v>-0.407</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2486</v>
+        <v>0.503</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0493</v>
+        <v>-0.91</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2322</v>
+        <v>0.4267</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3573</v>
+        <v>-0.6358</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.125</v>
+        <v>1.0625</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6365</v>
+        <v>-1.5054</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5933</v>
+        <v>-1.8828</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2298</v>
+        <v>0.3775</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3025</v>
+        <v>-0.4906</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5593</v>
+        <v>-0.572</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2569</v>
+        <v>0.0814</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-1.0148</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9661</v>
+        <v>-1.3109</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0271</v>
+        <v>0.2961</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.269</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0548</v>
+        <v>-0.1452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8658</v>
+        <v>-0.1238</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3282</v>
+        <v>0.6565</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3282</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4327</v>
+        <v>0.2778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1255</v>
+        <v>0.2539</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5582</v>
+        <v>0.024</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3452</v>
+        <v>-0.6365</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3859</v>
+        <v>0.5933</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0407</v>
+        <v>-1.2298</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7256</v>
+        <v>0.3025</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1106</v>
+        <v>1.5593</v>
       </c>
       <c r="L5" t="n">
-        <v>0.615</v>
+        <v>-1.2569</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3804</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7247</v>
+        <v>-0.9661</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.0271</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7433</v>
+        <v>-0.7654</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6347</v>
+        <v>-0.0486</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1086</v>
+        <v>-0.7168</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0553</v>
+        <v>-1.3615</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2645</v>
+        <v>-0.4713</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7909</v>
+        <v>-0.8902</v>
       </c>
       <c r="G6" t="n">
         <v>0.4111</v>
@@ -922,13 +922,13 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3751</v>
+        <v>0.0689</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0274</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8415</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1077</v>
+        <v>-1.4428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0336</v>
+        <v>-0.2766</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1413</v>
+        <v>-1.1662</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5254</v>
@@ -1000,13 +1000,13 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1269</v>
+        <v>-0.462</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1652</v>
+        <v>-0.1451</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2921</v>
+        <v>-0.3169</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2277</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5915</v>
+        <v>-1.7075</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.486</v>
+        <v>-2.2791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8945</v>
+        <v>0.5717</v>
       </c>
       <c r="G8" t="n">
         <v>-3.404</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3805</v>
+        <v>-0.4965</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9933</v>
+        <v>-0.7864</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6128</v>
+        <v>0.2899</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7046</v>
+        <v>-1.7457</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0397</v>
+        <v>-1.179</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6649</v>
+        <v>-0.5667</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2918</v>
+        <v>-2.0699</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8414</v>
+        <v>-2.158</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1332</v>
+        <v>0.0882</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5715</v>
+        <v>0.1797</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3248</v>
+        <v>0.2565</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7533</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8632</v>
+        <v>-2.2495</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4834</v>
+        <v>-2.4145</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3799</v>
+        <v>0.165</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3748</v>
+        <v>-0.7104</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9648</v>
+        <v>-0.4625</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.59</v>
+        <v>-0.2479</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9847</v>
+        <v>1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5133</v>
+        <v>1.2277</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5689</v>
+        <v>-1.9693</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9029</v>
+        <v>-0.4534</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.666</v>
+        <v>-1.5159</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0699</v>
+        <v>-2.2918</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.158</v>
+        <v>0.8414</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0882</v>
+        <v>-3.1332</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1797</v>
+        <v>0.5715</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2565</v>
+        <v>3.3248</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-2.7533</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2495</v>
+        <v>-2.8632</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4145</v>
+        <v>-2.4834</v>
       </c>
       <c r="O10" t="n">
-        <v>0.165</v>
+        <v>-0.3799</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>2.3169</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5337</v>
+        <v>0.1101</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1865</v>
+        <v>0.5511</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3472</v>
+        <v>-0.441</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2277</v>
+        <v>0.9847</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2277</v>
+        <v>1.5133</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5286</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5768</v>
+        <v>-4.0951</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6256</v>
+        <v>-2.9701</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-1.1249</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0785</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8147</v>
+        <v>0.2964</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0681</v>
+        <v>0.7236</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2534</v>
+        <v>-0.4272</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6991000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7705</v>
+        <v>-4.4643</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5114</v>
+        <v>-1.3046</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2591</v>
+        <v>-3.1597</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0225</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2926</v>
+        <v>0.0135</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3305</v>
+        <v>0.5373</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6231</v>
+        <v>-0.5238</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.2262</v>
+        <v>-14.2263</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.101100000000001</v>
+        <v>-6.100999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-8.125</v>
@@ -1438,7 +1438,7 @@
         <v>-9.9986</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.827</v>
+        <v>-6.826999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-0.5402</v>
@@ -1447,7 +1447,7 @@
         <v>3.7994</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.339799999999999</v>
+        <v>-4.3398</v>
       </c>
       <c r="M13" t="n">
         <v>-16.2854</v>
@@ -1468,16 +1468,16 @@
         <v>15.4462</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6213</v>
+        <v>-2.6214</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8234999999999999</v>
+        <v>0.8236000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.4448</v>
+        <v>-3.4449</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5711999999999999</v>
+        <v>-0.5712000000000002</v>
       </c>
       <c r="W13" t="n">
         <v>3.2696</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7985</v>
+        <v>5.7018</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9143</v>
+        <v>3.4314</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8842</v>
+        <v>2.2704</v>
       </c>
       <c r="G14" t="n">
         <v>1.7471</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.103</v>
+        <v>-0.1997</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0278</v>
+        <v>0.4893</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0753</v>
+        <v>-0.6891</v>
       </c>
       <c r="V14" t="n">
         <v>3.7683</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2792</v>
+        <v>4.7122</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0573</v>
+        <v>2.3897</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2219</v>
+        <v>2.3226</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0673</v>
+        <v>3.2848</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4892</v>
+        <v>1.786</v>
       </c>
       <c r="I15" t="n">
-        <v>1.578</v>
+        <v>1.4987</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4832</v>
+        <v>3.1832</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1801</v>
+        <v>2.4077</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3031</v>
+        <v>0.7754</v>
       </c>
       <c r="M15" t="n">
-        <v>0.584</v>
+        <v>0.1016</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6909</v>
+        <v>-0.6217</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2749</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="P15" t="n">
+        <v>0.7723</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.1585</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-3.0892</v>
       </c>
       <c r="R15" t="n">
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8998</v>
+        <v>0.6552</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1926</v>
+        <v>0.365</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.2902</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4707</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0902</v>
+        <v>4.1314</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0794</v>
+        <v>1.3675</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0108</v>
+        <v>2.7639</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2848</v>
+        <v>3.0673</v>
       </c>
       <c r="H16" t="n">
-        <v>1.786</v>
+        <v>1.4892</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4987</v>
+        <v>1.578</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1832</v>
+        <v>2.4832</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4077</v>
+        <v>2.1801</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7754</v>
+        <v>0.3031</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1016</v>
+        <v>0.584</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6217</v>
+        <v>-0.6909</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7233000000000001</v>
+        <v>1.2749</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R16" t="n">
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0332</v>
+        <v>0.752</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0547</v>
+        <v>0.5029</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0215</v>
+        <v>0.2491</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4707</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9837</v>
+        <v>2.7204</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5494</v>
+        <v>0.8254</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4343</v>
+        <v>1.895</v>
       </c>
       <c r="G17" t="n">
         <v>6.4012</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8495</v>
+        <v>0.5863</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7371</v>
+        <v>1.0132</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.4269</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9847</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4882</v>
+        <v>2.2413</v>
       </c>
       <c r="E18" t="n">
-        <v>2.808</v>
+        <v>2.4978</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3198</v>
+        <v>-0.2564</v>
       </c>
       <c r="G18" t="n">
         <v>4.5244</v>
@@ -1858,13 +1858,13 @@
         <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9984</v>
+        <v>0.7516</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7718</v>
+        <v>0.4616</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2266</v>
+        <v>0.29</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4554</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9683</v>
+        <v>0.9228</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2612</v>
+        <v>1.3646</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2928</v>
+        <v>-0.4418</v>
       </c>
       <c r="G19" t="n">
         <v>1.0949</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1266</v>
+        <v>-0.1722</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0277</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.099</v>
+        <v>-0.248</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4807</v>
+        <v>0.3773</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1324</v>
+        <v>2.029</v>
       </c>
       <c r="F20" t="n">
         <v>-1.6517</v>
@@ -2014,10 +2014,10 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3863</v>
+        <v>0.2829</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7997</v>
+        <v>0.6963</v>
       </c>
       <c r="U20" t="n">
         <v>-0.4135</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1147</v>
+        <v>-0.1251</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.118</v>
+        <v>-0.5317</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2327</v>
+        <v>0.4065</v>
       </c>
       <c r="G21" t="n">
         <v>0.1645</v>
@@ -2092,13 +2092,13 @@
         <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5295</v>
+        <v>0.2896</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4136</v>
+        <v>-0.0001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1159</v>
+        <v>0.2897</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.48</v>
+        <v>-1.3517</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0206</v>
+        <v>-0.9172</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4594</v>
+        <v>-0.4346</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4759</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0386</v>
+        <v>0.0896</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5772</v>
+        <v>-1.5732</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6418</v>
+        <v>-1.5384</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0645</v>
+        <v>-0.0348</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9248</v>
@@ -2248,13 +2248,13 @@
         <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1545</v>
+        <v>0.1586</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3477</v>
+        <v>0.2484</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9202</v>
+        <v>-2.8417</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8966</v>
+        <v>-2.7931</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0237</v>
+        <v>-0.0485</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1519</v>
@@ -2326,13 +2326,13 @@
         <v>0.1931</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0386</v>
+        <v>0.1172</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2594</v>
+        <v>0.2345</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.2261</v>
+        <v>14.9155</v>
       </c>
       <c r="E25" t="n">
-        <v>8.125000000000002</v>
+        <v>8.125</v>
       </c>
       <c r="F25" t="n">
-        <v>6.101000000000002</v>
+        <v>6.7906</v>
       </c>
       <c r="G25" t="n">
         <v>16.826</v>
@@ -2386,7 +2386,7 @@
         <v>2.4873</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5403</v>
+        <v>0.5403000000000004</v>
       </c>
       <c r="N25" t="n">
         <v>-3.7996</v>
@@ -2404,19 +2404,19 @@
         <v>9.654</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6216</v>
+        <v>3.3111</v>
       </c>
       <c r="T25" t="n">
-        <v>3.444900000000001</v>
+        <v>3.4451</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8234999999999995</v>
+        <v>-0.1342</v>
       </c>
       <c r="V25" t="n">
         <v>0.5711999999999997</v>
       </c>
       <c r="W25" t="n">
-        <v>3.840799999999999</v>
+        <v>3.8408</v>
       </c>
       <c r="X25" t="n">
         <v>-3.2696</v>
